--- a/output/topology_excel/4571.xlsx
+++ b/output/topology_excel/4571.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -674,10 +674,10 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>318</v>
+        <v>69</v>
       </c>
       <c r="F11" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12">
@@ -685,7 +685,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -696,18 +696,18 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>180</v>
+        <v>144</v>
       </c>
       <c r="F12" t="n">
-        <v>171</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -718,18 +718,18 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F13" t="n">
-        <v>67</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +751,7 @@
         <v>2</v>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>145</v>
+        <v>263</v>
       </c>
       <c r="F15" t="n">
         <v>11</v>
@@ -770,10 +770,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -784,18 +784,18 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>207</v>
+        <v>104</v>
       </c>
       <c r="F16" t="n">
-        <v>127</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="F17" t="n">
         <v>12</v>
@@ -817,7 +817,7 @@
         <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,10 +828,10 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>162</v>
+        <v>207</v>
       </c>
       <c r="F18" t="n">
-        <v>155</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19">
@@ -839,7 +839,7 @@
         <v>3</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,18 +850,18 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="F19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>263</v>
+        <v>144</v>
       </c>
       <c r="F20" t="n">
         <v>11</v>
@@ -880,11 +880,11 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" t="n">
         <v>5</v>
       </c>
-      <c r="B21" t="n">
-        <v>6</v>
-      </c>
       <c r="C21" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -894,18 +894,18 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>145</v>
+        <v>288</v>
       </c>
       <c r="F21" t="n">
-        <v>12</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B22" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>104</v>
+        <v>264</v>
       </c>
       <c r="F22" t="n">
-        <v>12</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23">
@@ -927,7 +927,7 @@
         <v>6</v>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,10 +938,10 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>96</v>
+        <v>177</v>
       </c>
       <c r="F23" t="n">
-        <v>12</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24">
@@ -949,7 +949,7 @@
         <v>7</v>
       </c>
       <c r="B24" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -960,15 +960,15 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>144</v>
+        <v>96</v>
       </c>
       <c r="F24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B25" t="n">
         <v>11</v>
@@ -982,7 +982,7 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="F25" t="n">
         <v>12</v>
@@ -990,24 +990,222 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" t="n">
         <v>9</v>
       </c>
-      <c r="B26" t="n">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>145</v>
+      </c>
+      <c r="F26" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" t="n">
+        <v>15</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>11</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>9</v>
+      </c>
+      <c r="B28" t="n">
+        <v>13</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>201</v>
+      </c>
+      <c r="F28" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>9</v>
+      </c>
+      <c r="B29" t="n">
         <v>10</v>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" t="n">
-        <v>288</v>
-      </c>
-      <c r="F26" t="n">
-        <v>69</v>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>181</v>
+      </c>
+      <c r="F29" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11</v>
+      </c>
+      <c r="B30" t="n">
+        <v>15</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>104</v>
+      </c>
+      <c r="F30" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>13</v>
+      </c>
+      <c r="B31" t="n">
+        <v>15</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>59</v>
+      </c>
+      <c r="F31" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14</v>
+      </c>
+      <c r="B32" t="n">
+        <v>15</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>114</v>
+      </c>
+      <c r="F32" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>212</v>
+      </c>
+      <c r="F33" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>6</v>
+      </c>
+      <c r="B34" t="n">
+        <v>15</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>88</v>
+      </c>
+      <c r="F34" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>9</v>
+      </c>
+      <c r="B35" t="n">
+        <v>13</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>98</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/4571.xlsx
+++ b/output/topology_excel/4571.xlsx
@@ -451,12 +451,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
         <v>69</v>
       </c>
       <c r="F11" t="n">
-        <v>67</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -699,7 +699,7 @@
         <v>144</v>
       </c>
       <c r="F12" t="n">
-        <v>66</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -831,7 +831,7 @@
         <v>207</v>
       </c>
       <c r="F18" t="n">
-        <v>127</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -897,7 +897,7 @@
         <v>288</v>
       </c>
       <c r="F21" t="n">
-        <v>69</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -919,7 +919,7 @@
         <v>264</v>
       </c>
       <c r="F22" t="n">
-        <v>78</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
@@ -941,7 +941,7 @@
         <v>177</v>
       </c>
       <c r="F23" t="n">
-        <v>62</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -1095,7 +1095,7 @@
         <v>104</v>
       </c>
       <c r="F30" t="n">
-        <v>67</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31">
@@ -1117,7 +1117,7 @@
         <v>59</v>
       </c>
       <c r="F31" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32">
@@ -1139,7 +1139,7 @@
         <v>114</v>
       </c>
       <c r="F32" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33">
